--- a/pages/CdA Testing/FullRunSheet.xlsx
+++ b/pages/CdA Testing/FullRunSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F6264B-BD24-4860-89A6-466AEA9425AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF26E14-59C2-49B8-96A1-3A4DAC9D0511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{C4EF7516-2B37-40B4-B22F-A762B428A288}"/>
   </bookViews>

--- a/pages/CdA Testing/FullRunSheet.xlsx
+++ b/pages/CdA Testing/FullRunSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF26E14-59C2-49B8-96A1-3A4DAC9D0511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9304AD0-62EF-47BB-B7BE-13FE539ADAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{C4EF7516-2B37-40B4-B22F-A762B428A288}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="81">
   <si>
     <t>Album</t>
   </si>
@@ -208,12 +208,234 @@
   <si>
     <t>Run</t>
   </si>
+  <si>
+    <t>23-10-11 Bryony Botha Side On</t>
+  </si>
+  <si>
+    <t>1. Current Position + Current Equipment (LeCol, Mistral L)</t>
+  </si>
+  <si>
+    <t>2. Position 1 - (long and low stack 25deg - LL25) - LeCol Suit - Mistral (L)</t>
+  </si>
+  <si>
+    <t>3. Position 1 - (long and low stack 25deg - LL25) - LeCol Suit - POC (L)</t>
+  </si>
+  <si>
+    <t>4. Position 2 - (short and high - SH22) - LeCol Suit - POC (L)</t>
+  </si>
+  <si>
+    <t>5. Position 2 - (short and high - SH22) - LeCol Suit - Mistral (L)</t>
+  </si>
+  <si>
+    <t>6. Position 3 - (short and mid-range 22deg - S22) - LeCol Suit - Mistral (L)</t>
+  </si>
+  <si>
+    <t>7. Position 4 - (short and mid-range 25deg - S25) - LeCol Suit - Mistral (L)</t>
+  </si>
+  <si>
+    <t>8. Best position + Helmet Option 4 (Sweet Protection)</t>
+  </si>
+  <si>
+    <t>9. Best position + Helmet Option 5 (Specialized)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">10. Suit-A1/ECLO2-pants - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P10 Undervest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - (best position LL25 + best helmet Mistral (L))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11. Suit-A1/ECLO2-pants -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Rule28 Undervest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - (best position LL25 + best helmet Mistral (L))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">12. Suit-B3/LNM-pants - TENSION Low - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Undervest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - (best position LL25 + best helmet Mistral (L))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">13. Suit-B3/LNM-pants - TENSION High </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- P10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Undervest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - (best position LL25 + best helmet Mistral (L))</t>
+    </r>
+  </si>
+  <si>
+    <t>14. Suit-A5/ECLO2-pants - Original Print Setting - (best position LL25 + best helmet Mistral (L))</t>
+  </si>
+  <si>
+    <t>15. Suit-A5/ECLO2-pants - Virgin Fabric - (best position LL25 + best helmet Mistral (L))</t>
+  </si>
+  <si>
+    <t>16. Suit-A10/ECLO2-pants - TRIP LOCATION 1 - (best position LL25 + best helmet Mistral (L))</t>
+  </si>
+  <si>
+    <t>17. Suit-A10/ECLO2-pants - TRIP LOCATION 2 - (best position LL25 + best helmet Mistral (L))</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">18. Suit-A1/ECLO2-pants - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P10 Undervest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - (best position LL25 + best helmet Mistral (L))</t>
+    </r>
+  </si>
+  <si>
+    <t>19. Miti-Overshoes - (best position LL25 + best helmet Mistral (L) + best suit Suit-A1/ECLO2)</t>
+  </si>
+  <si>
+    <t>20. ImpSport-Overshoes - (best position LL25 + best helmet Mistral (L) + best suit Suit-A1/ECLO2)</t>
+  </si>
+  <si>
+    <t>21. Best system configuration (best position LL25 + Suit-A1/ECLO2 + ImpSport) KASK Mistral LW</t>
+  </si>
+  <si>
+    <t>22. Bike only Current Bars</t>
+  </si>
+  <si>
+    <t>0. Bike only Current Bars</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,6 +451,20 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -266,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -280,6 +516,7 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -594,11 +831,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0519FE8-7E25-488D-A25B-6D59627E68B4}">
-  <dimension ref="A1:I355"/>
+  <dimension ref="A1:I517"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="34.109375" customWidth="1"/>
+    <col min="2" max="2" width="89.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="34.109375" customWidth="1"/>
     <col min="7" max="7" width="97" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -7507,13 +7745,2341 @@
       <c r="A355" t="s">
         <v>55</v>
       </c>
-      <c r="B355" t="s">
+      <c r="G355" t="s">
         <v>32</v>
       </c>
       <c r="H355">
         <v>92</v>
       </c>
       <c r="I355">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>57</v>
+      </c>
+      <c r="G356" t="s">
+        <v>80</v>
+      </c>
+      <c r="H356">
+        <v>6</v>
+      </c>
+      <c r="I356">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>57</v>
+      </c>
+      <c r="B357" s="5"/>
+      <c r="G357" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H357">
+        <v>7</v>
+      </c>
+      <c r="I357">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>57</v>
+      </c>
+      <c r="B358" s="5"/>
+      <c r="G358" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H358">
+        <v>8</v>
+      </c>
+      <c r="I358">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>57</v>
+      </c>
+      <c r="B359" s="5"/>
+      <c r="G359" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H359">
+        <v>9</v>
+      </c>
+      <c r="I359">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>57</v>
+      </c>
+      <c r="B360" s="5"/>
+      <c r="G360" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H360">
+        <v>10</v>
+      </c>
+      <c r="I360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>57</v>
+      </c>
+      <c r="B361" s="5"/>
+      <c r="G361" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H361">
+        <v>11</v>
+      </c>
+      <c r="I361">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>57</v>
+      </c>
+      <c r="B362" s="5"/>
+      <c r="G362" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H362">
+        <v>12</v>
+      </c>
+      <c r="I362">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>57</v>
+      </c>
+      <c r="B363" s="5"/>
+      <c r="G363" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H363">
+        <v>13</v>
+      </c>
+      <c r="I363">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>57</v>
+      </c>
+      <c r="B364" s="5"/>
+      <c r="G364" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H364">
+        <v>14</v>
+      </c>
+      <c r="I364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>57</v>
+      </c>
+      <c r="B365" s="5"/>
+      <c r="G365" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H365">
+        <v>15</v>
+      </c>
+      <c r="I365">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>57</v>
+      </c>
+      <c r="G366" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H366">
+        <v>16</v>
+      </c>
+      <c r="I366">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>57</v>
+      </c>
+      <c r="G367" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H367">
+        <v>17</v>
+      </c>
+      <c r="I367">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>57</v>
+      </c>
+      <c r="G368" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H368">
+        <v>18</v>
+      </c>
+      <c r="I368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>57</v>
+      </c>
+      <c r="G369" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H369">
+        <v>19</v>
+      </c>
+      <c r="I369">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>57</v>
+      </c>
+      <c r="G370" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H370">
+        <v>20</v>
+      </c>
+      <c r="I370">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>57</v>
+      </c>
+      <c r="G371" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H371">
+        <v>21</v>
+      </c>
+      <c r="I371">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>57</v>
+      </c>
+      <c r="G372" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H372">
+        <v>22</v>
+      </c>
+      <c r="I372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>57</v>
+      </c>
+      <c r="B373" s="5"/>
+      <c r="G373" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H373">
+        <v>23</v>
+      </c>
+      <c r="I373">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>57</v>
+      </c>
+      <c r="G374" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H374">
+        <v>24</v>
+      </c>
+      <c r="I374">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>57</v>
+      </c>
+      <c r="G375" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H375">
+        <v>25</v>
+      </c>
+      <c r="I375">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>57</v>
+      </c>
+      <c r="G376" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H376">
+        <v>26</v>
+      </c>
+      <c r="I376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>57</v>
+      </c>
+      <c r="B377" s="5"/>
+      <c r="G377" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H377">
+        <v>27</v>
+      </c>
+      <c r="I377">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>57</v>
+      </c>
+      <c r="G378" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H378">
+        <v>28</v>
+      </c>
+      <c r="I378">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>57</v>
+      </c>
+      <c r="G379" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H379">
+        <v>29</v>
+      </c>
+      <c r="I379">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>57</v>
+      </c>
+      <c r="G380" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H380">
+        <v>30</v>
+      </c>
+      <c r="I380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>57</v>
+      </c>
+      <c r="B381" s="5"/>
+      <c r="G381" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H381">
+        <v>31</v>
+      </c>
+      <c r="I381">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>57</v>
+      </c>
+      <c r="G382" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H382">
+        <v>32</v>
+      </c>
+      <c r="I382">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>57</v>
+      </c>
+      <c r="G383" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H383">
+        <v>33</v>
+      </c>
+      <c r="I383">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>57</v>
+      </c>
+      <c r="G384" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H384">
+        <v>34</v>
+      </c>
+      <c r="I384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>57</v>
+      </c>
+      <c r="G385" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H385">
+        <v>35</v>
+      </c>
+      <c r="I385">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>57</v>
+      </c>
+      <c r="G386" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H386">
+        <v>36</v>
+      </c>
+      <c r="I386">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>57</v>
+      </c>
+      <c r="B387" s="5"/>
+      <c r="G387" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H387">
+        <v>37</v>
+      </c>
+      <c r="I387">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>57</v>
+      </c>
+      <c r="B388" s="5"/>
+      <c r="G388" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H388">
+        <v>38</v>
+      </c>
+      <c r="I388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>57</v>
+      </c>
+      <c r="B389" s="5"/>
+      <c r="G389" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H389">
+        <v>39</v>
+      </c>
+      <c r="I389">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>57</v>
+      </c>
+      <c r="G390" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H390">
+        <v>40</v>
+      </c>
+      <c r="I390">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>57</v>
+      </c>
+      <c r="G391" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H391">
+        <v>41</v>
+      </c>
+      <c r="I391">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>57</v>
+      </c>
+      <c r="G392" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H392">
+        <v>42</v>
+      </c>
+      <c r="I392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>57</v>
+      </c>
+      <c r="G393" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H393">
+        <v>43</v>
+      </c>
+      <c r="I393">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>57</v>
+      </c>
+      <c r="G394" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H394">
+        <v>44</v>
+      </c>
+      <c r="I394">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>57</v>
+      </c>
+      <c r="G395" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H395">
+        <v>45</v>
+      </c>
+      <c r="I395">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>57</v>
+      </c>
+      <c r="B396" s="5"/>
+      <c r="G396" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H396">
+        <v>46</v>
+      </c>
+      <c r="I396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>57</v>
+      </c>
+      <c r="B397" s="7"/>
+      <c r="G397" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H397">
+        <v>47</v>
+      </c>
+      <c r="I397">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>57</v>
+      </c>
+      <c r="G398" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H398">
+        <v>48</v>
+      </c>
+      <c r="I398">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>57</v>
+      </c>
+      <c r="G399" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H399">
+        <v>49</v>
+      </c>
+      <c r="I399">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>57</v>
+      </c>
+      <c r="G400" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H400">
+        <v>50</v>
+      </c>
+      <c r="I400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>57</v>
+      </c>
+      <c r="G401" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H401">
+        <v>51</v>
+      </c>
+      <c r="I401">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>57</v>
+      </c>
+      <c r="G402" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H402">
+        <v>52</v>
+      </c>
+      <c r="I402">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>57</v>
+      </c>
+      <c r="G403" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H403">
+        <v>53</v>
+      </c>
+      <c r="I403">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>57</v>
+      </c>
+      <c r="B404" s="5"/>
+      <c r="G404" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H404">
+        <v>54</v>
+      </c>
+      <c r="I404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>57</v>
+      </c>
+      <c r="B405" s="4"/>
+      <c r="G405" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H405">
+        <v>55</v>
+      </c>
+      <c r="I405">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>57</v>
+      </c>
+      <c r="G406" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H406">
+        <v>56</v>
+      </c>
+      <c r="I406">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>57</v>
+      </c>
+      <c r="G407" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H407">
+        <v>57</v>
+      </c>
+      <c r="I407">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>57</v>
+      </c>
+      <c r="G408" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H408">
+        <v>58</v>
+      </c>
+      <c r="I408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>57</v>
+      </c>
+      <c r="G409" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H409">
+        <v>59</v>
+      </c>
+      <c r="I409">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>57</v>
+      </c>
+      <c r="G410" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H410">
+        <v>60</v>
+      </c>
+      <c r="I410">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>57</v>
+      </c>
+      <c r="B411" s="4"/>
+      <c r="G411" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H411">
+        <v>61</v>
+      </c>
+      <c r="I411">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>57</v>
+      </c>
+      <c r="B412" s="4"/>
+      <c r="G412" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H412">
+        <v>62</v>
+      </c>
+      <c r="I412">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>57</v>
+      </c>
+      <c r="G413" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H413">
+        <v>63</v>
+      </c>
+      <c r="I413">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>57</v>
+      </c>
+      <c r="G414" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H414">
+        <v>64</v>
+      </c>
+      <c r="I414">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>57</v>
+      </c>
+      <c r="G415" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H415">
+        <v>65</v>
+      </c>
+      <c r="I415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>57</v>
+      </c>
+      <c r="G416" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H416">
+        <v>66</v>
+      </c>
+      <c r="I416">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>57</v>
+      </c>
+      <c r="G417" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H417">
+        <v>67</v>
+      </c>
+      <c r="I417">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>57</v>
+      </c>
+      <c r="G418" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H418">
+        <v>68</v>
+      </c>
+      <c r="I418">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>57</v>
+      </c>
+      <c r="B419" s="5"/>
+      <c r="G419" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H419">
+        <v>69</v>
+      </c>
+      <c r="I419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>57</v>
+      </c>
+      <c r="B420" s="4"/>
+      <c r="G420" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H420">
+        <v>70</v>
+      </c>
+      <c r="I420">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>57</v>
+      </c>
+      <c r="G421" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H421">
+        <v>71</v>
+      </c>
+      <c r="I421">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>57</v>
+      </c>
+      <c r="G422" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H422">
+        <v>72</v>
+      </c>
+      <c r="I422">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>57</v>
+      </c>
+      <c r="G423" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H423">
+        <v>73</v>
+      </c>
+      <c r="I423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>57</v>
+      </c>
+      <c r="G424" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H424">
+        <v>74</v>
+      </c>
+      <c r="I424">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>57</v>
+      </c>
+      <c r="G425" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H425">
+        <v>75</v>
+      </c>
+      <c r="I425">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>57</v>
+      </c>
+      <c r="G426" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H426">
+        <v>76</v>
+      </c>
+      <c r="I426">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>57</v>
+      </c>
+      <c r="B427" s="4"/>
+      <c r="G427" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H427">
+        <v>77</v>
+      </c>
+      <c r="I427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>57</v>
+      </c>
+      <c r="B428" s="4"/>
+      <c r="G428" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H428">
+        <v>78</v>
+      </c>
+      <c r="I428">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>57</v>
+      </c>
+      <c r="G429" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H429">
+        <v>79</v>
+      </c>
+      <c r="I429">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>57</v>
+      </c>
+      <c r="G430" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H430">
+        <v>80</v>
+      </c>
+      <c r="I430">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>57</v>
+      </c>
+      <c r="G431" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H431">
+        <v>81</v>
+      </c>
+      <c r="I431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>57</v>
+      </c>
+      <c r="B432" s="4"/>
+      <c r="G432" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H432">
+        <v>82</v>
+      </c>
+      <c r="I432">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>57</v>
+      </c>
+      <c r="G433" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H433">
+        <v>83</v>
+      </c>
+      <c r="I433">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>57</v>
+      </c>
+      <c r="G434" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H434">
+        <v>84</v>
+      </c>
+      <c r="I434">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>57</v>
+      </c>
+      <c r="G435" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H435">
+        <v>85</v>
+      </c>
+      <c r="I435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>57</v>
+      </c>
+      <c r="G436" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H436">
+        <v>86</v>
+      </c>
+      <c r="I436">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>57</v>
+      </c>
+      <c r="G437" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H437">
+        <v>87</v>
+      </c>
+      <c r="I437">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>57</v>
+      </c>
+      <c r="G438" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H438">
+        <v>88</v>
+      </c>
+      <c r="I438">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>57</v>
+      </c>
+      <c r="B439" s="4"/>
+      <c r="G439" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H439">
+        <v>89</v>
+      </c>
+      <c r="I439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>57</v>
+      </c>
+      <c r="B440" s="4"/>
+      <c r="G440" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H440">
+        <v>90</v>
+      </c>
+      <c r="I440">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>57</v>
+      </c>
+      <c r="G441" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H441">
+        <v>91</v>
+      </c>
+      <c r="I441">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>57</v>
+      </c>
+      <c r="G442" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H442">
+        <v>92</v>
+      </c>
+      <c r="I442">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>57</v>
+      </c>
+      <c r="G443" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H443">
+        <v>93</v>
+      </c>
+      <c r="I443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>57</v>
+      </c>
+      <c r="G444" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H444">
+        <v>94</v>
+      </c>
+      <c r="I444">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>57</v>
+      </c>
+      <c r="G445" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H445">
+        <v>95</v>
+      </c>
+      <c r="I445">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>57</v>
+      </c>
+      <c r="G446" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H446">
+        <v>96</v>
+      </c>
+      <c r="I446">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>57</v>
+      </c>
+      <c r="B447" s="4"/>
+      <c r="G447" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H447">
+        <v>97</v>
+      </c>
+      <c r="I447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>57</v>
+      </c>
+      <c r="B448" s="4"/>
+      <c r="G448" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H448">
+        <v>99</v>
+      </c>
+      <c r="I448">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>57</v>
+      </c>
+      <c r="G449" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H449">
+        <v>100</v>
+      </c>
+      <c r="I449">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>57</v>
+      </c>
+      <c r="G450" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H450">
+        <v>101</v>
+      </c>
+      <c r="I450">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>57</v>
+      </c>
+      <c r="G451" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H451">
+        <v>102</v>
+      </c>
+      <c r="I451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>57</v>
+      </c>
+      <c r="G452" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H452">
+        <v>103</v>
+      </c>
+      <c r="I452">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>57</v>
+      </c>
+      <c r="G453" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H453">
+        <v>104</v>
+      </c>
+      <c r="I453">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>57</v>
+      </c>
+      <c r="G454" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H454">
+        <v>105</v>
+      </c>
+      <c r="I454">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>57</v>
+      </c>
+      <c r="B455" s="4"/>
+      <c r="G455" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H455">
+        <v>106</v>
+      </c>
+      <c r="I455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>57</v>
+      </c>
+      <c r="B456" s="4"/>
+      <c r="G456" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H456">
+        <v>107</v>
+      </c>
+      <c r="I456">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>57</v>
+      </c>
+      <c r="B457" s="4"/>
+      <c r="G457" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H457">
+        <v>108</v>
+      </c>
+      <c r="I457">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>57</v>
+      </c>
+      <c r="G458" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H458">
+        <v>109</v>
+      </c>
+      <c r="I458">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>57</v>
+      </c>
+      <c r="G459" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H459">
+        <v>110</v>
+      </c>
+      <c r="I459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>57</v>
+      </c>
+      <c r="G460" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H460">
+        <v>111</v>
+      </c>
+      <c r="I460">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>57</v>
+      </c>
+      <c r="G461" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H461">
+        <v>112</v>
+      </c>
+      <c r="I461">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>57</v>
+      </c>
+      <c r="G462" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H462">
+        <v>113</v>
+      </c>
+      <c r="I462">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>57</v>
+      </c>
+      <c r="G463" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H463">
+        <v>114</v>
+      </c>
+      <c r="I463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>57</v>
+      </c>
+      <c r="B464" s="4"/>
+      <c r="G464" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H464">
+        <v>115</v>
+      </c>
+      <c r="I464">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>57</v>
+      </c>
+      <c r="B465" s="4"/>
+      <c r="G465" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H465">
+        <v>116</v>
+      </c>
+      <c r="I465">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>57</v>
+      </c>
+      <c r="B466" s="4"/>
+      <c r="G466" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H466">
+        <v>117</v>
+      </c>
+      <c r="I466">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>57</v>
+      </c>
+      <c r="G467" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H467">
+        <v>118</v>
+      </c>
+      <c r="I467">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>57</v>
+      </c>
+      <c r="B468" s="4"/>
+      <c r="G468" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H468">
+        <v>119</v>
+      </c>
+      <c r="I468">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>57</v>
+      </c>
+      <c r="B469" s="4"/>
+      <c r="G469" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H469">
+        <v>120</v>
+      </c>
+      <c r="I469">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>57</v>
+      </c>
+      <c r="B470" s="4"/>
+      <c r="G470" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H470">
+        <v>121</v>
+      </c>
+      <c r="I470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>57</v>
+      </c>
+      <c r="B471" s="4"/>
+      <c r="G471" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H471">
+        <v>122</v>
+      </c>
+      <c r="I471">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>57</v>
+      </c>
+      <c r="B472" s="4"/>
+      <c r="G472" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H472">
+        <v>123</v>
+      </c>
+      <c r="I472">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>57</v>
+      </c>
+      <c r="G473" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H473">
+        <v>125</v>
+      </c>
+      <c r="I473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>57</v>
+      </c>
+      <c r="B474" s="4"/>
+      <c r="G474" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H474">
+        <v>126</v>
+      </c>
+      <c r="I474">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="475" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>57</v>
+      </c>
+      <c r="B475" s="4"/>
+      <c r="G475" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H475">
+        <v>127</v>
+      </c>
+      <c r="I475">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>57</v>
+      </c>
+      <c r="B476" s="4"/>
+      <c r="G476" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H476">
+        <v>128</v>
+      </c>
+      <c r="I476">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>57</v>
+      </c>
+      <c r="B477" s="4"/>
+      <c r="G477" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H477">
+        <v>129</v>
+      </c>
+      <c r="I477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>57</v>
+      </c>
+      <c r="B478" s="4"/>
+      <c r="G478" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H478">
+        <v>130</v>
+      </c>
+      <c r="I478">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>57</v>
+      </c>
+      <c r="B479" s="4"/>
+      <c r="G479" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H479">
+        <v>131</v>
+      </c>
+      <c r="I479">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>57</v>
+      </c>
+      <c r="G480" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H480">
+        <v>132</v>
+      </c>
+      <c r="I480">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>57</v>
+      </c>
+      <c r="B481" s="4"/>
+      <c r="G481" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H481">
+        <v>133</v>
+      </c>
+      <c r="I481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>57</v>
+      </c>
+      <c r="B482" s="4"/>
+      <c r="G482" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H482">
+        <v>134</v>
+      </c>
+      <c r="I482">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>57</v>
+      </c>
+      <c r="B483" s="4"/>
+      <c r="G483" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H483">
+        <v>135</v>
+      </c>
+      <c r="I483">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>57</v>
+      </c>
+      <c r="G484" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H484">
+        <v>136</v>
+      </c>
+      <c r="I484">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>57</v>
+      </c>
+      <c r="G485" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H485">
+        <v>137</v>
+      </c>
+      <c r="I485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>57</v>
+      </c>
+      <c r="G486" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H486">
+        <v>138</v>
+      </c>
+      <c r="I486">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="487" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>57</v>
+      </c>
+      <c r="G487" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H487">
+        <v>139</v>
+      </c>
+      <c r="I487">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="488" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>57</v>
+      </c>
+      <c r="G488" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H488">
+        <v>140</v>
+      </c>
+      <c r="I488">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="489" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>57</v>
+      </c>
+      <c r="G489" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H489">
+        <v>141</v>
+      </c>
+      <c r="I489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>57</v>
+      </c>
+      <c r="B490" s="4"/>
+      <c r="G490" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H490">
+        <v>142</v>
+      </c>
+      <c r="I490">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>57</v>
+      </c>
+      <c r="B491" s="4"/>
+      <c r="G491" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H491">
+        <v>143</v>
+      </c>
+      <c r="I491">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="492" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>57</v>
+      </c>
+      <c r="G492" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H492">
+        <v>144</v>
+      </c>
+      <c r="I492">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>57</v>
+      </c>
+      <c r="G493" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H493">
+        <v>145</v>
+      </c>
+      <c r="I493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>57</v>
+      </c>
+      <c r="G494" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H494">
+        <v>146</v>
+      </c>
+      <c r="I494">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="495" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>57</v>
+      </c>
+      <c r="G495" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H495">
+        <v>147</v>
+      </c>
+      <c r="I495">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="496" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>57</v>
+      </c>
+      <c r="G496" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H496">
+        <v>148</v>
+      </c>
+      <c r="I496">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>57</v>
+      </c>
+      <c r="B497" s="4"/>
+      <c r="G497" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H497">
+        <v>149</v>
+      </c>
+      <c r="I497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>57</v>
+      </c>
+      <c r="B498" s="4"/>
+      <c r="G498" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H498">
+        <v>150</v>
+      </c>
+      <c r="I498">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>57</v>
+      </c>
+      <c r="B499" s="4"/>
+      <c r="G499" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H499">
+        <v>151</v>
+      </c>
+      <c r="I499">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>57</v>
+      </c>
+      <c r="B500" s="4"/>
+      <c r="G500" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H500">
+        <v>152</v>
+      </c>
+      <c r="I500">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="501" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>57</v>
+      </c>
+      <c r="G501" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H501">
+        <v>153</v>
+      </c>
+      <c r="I501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>57</v>
+      </c>
+      <c r="G502" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H502">
+        <v>154</v>
+      </c>
+      <c r="I502">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="503" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>57</v>
+      </c>
+      <c r="G503" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H503">
+        <v>155</v>
+      </c>
+      <c r="I503">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="504" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>57</v>
+      </c>
+      <c r="G504" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H504">
+        <v>157</v>
+      </c>
+      <c r="I504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>57</v>
+      </c>
+      <c r="G505" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H505">
+        <v>158</v>
+      </c>
+      <c r="I505">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="506" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A506" t="s">
+        <v>57</v>
+      </c>
+      <c r="G506" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H506">
+        <v>159</v>
+      </c>
+      <c r="I506">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A507" t="s">
+        <v>57</v>
+      </c>
+      <c r="B507" s="4"/>
+      <c r="G507" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H507">
+        <v>160</v>
+      </c>
+      <c r="I507">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A508" t="s">
+        <v>57</v>
+      </c>
+      <c r="B508" s="4"/>
+      <c r="G508" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H508">
+        <v>161</v>
+      </c>
+      <c r="I508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>57</v>
+      </c>
+      <c r="B509" s="4"/>
+      <c r="G509" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H509">
+        <v>162</v>
+      </c>
+      <c r="I509">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A510" t="s">
+        <v>57</v>
+      </c>
+      <c r="B510" s="4"/>
+      <c r="G510" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H510">
+        <v>163</v>
+      </c>
+      <c r="I510">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>57</v>
+      </c>
+      <c r="G511" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H511">
+        <v>164</v>
+      </c>
+      <c r="I511">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>57</v>
+      </c>
+      <c r="G512" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H512">
+        <v>165</v>
+      </c>
+      <c r="I512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>57</v>
+      </c>
+      <c r="G513" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H513">
+        <v>166</v>
+      </c>
+      <c r="I513">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>57</v>
+      </c>
+      <c r="G514" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H514">
+        <v>167</v>
+      </c>
+      <c r="I514">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>57</v>
+      </c>
+      <c r="G515" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H515">
+        <v>168</v>
+      </c>
+      <c r="I515">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>57</v>
+      </c>
+      <c r="G516" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H516">
+        <v>169</v>
+      </c>
+      <c r="I516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>57</v>
+      </c>
+      <c r="G517" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H517">
+        <v>170</v>
+      </c>
+      <c r="I517">
         <v>12</v>
       </c>
     </row>

--- a/pages/CdA Testing/FullRunSheet.xlsx
+++ b/pages/CdA Testing/FullRunSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9304AD0-62EF-47BB-B7BE-13FE539ADAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C8B74C-BCC9-4F0D-A94C-AF57915AFDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{C4EF7516-2B37-40B4-B22F-A762B428A288}"/>
+    <workbookView xWindow="10704" yWindow="0" windowWidth="12300" windowHeight="12504" xr2:uid="{C4EF7516-2B37-40B4-B22F-A762B428A288}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="103">
   <si>
     <t>Album</t>
   </si>
@@ -430,6 +430,72 @@
   <si>
     <t>0. Bike only Current Bars</t>
   </si>
+  <si>
+    <t>23-10-10 Ellesse Andrews Side On</t>
+  </si>
+  <si>
+    <t>2. Suit-B1/LNM-Pants + Tiana 10 Under-Vest (current)</t>
+  </si>
+  <si>
+    <t>3. Suit-C1/PU-Pants + Tiana 10 Under-Vest (high tension suit - T#2)</t>
+  </si>
+  <si>
+    <t>4. Suit-C1/PU-Pants + Tiana 10 Under-Vest (medium tension suit - T#1) - Current Position</t>
+  </si>
+  <si>
+    <t>5. Suit-C1/PU-Pants + Tiana 10 Under-Vest  (low tension suit - T#0.5) - Current Position</t>
+  </si>
+  <si>
+    <t>6. Suit-C1/PU-Pants + Payen 10 Under-Vest (high tension suit - T#2) - Current Position</t>
+  </si>
+  <si>
+    <t>7. Suit-C1/PU-Pants + Payen 5 Under-Vest (high tension suit - T#2) - Current Position</t>
+  </si>
+  <si>
+    <t>8. Suit-C1/PU-Pants + Payen 15 Under-Vest (high tension suit - T#2) - Current Position</t>
+  </si>
+  <si>
+    <t>9. Suit-C3/PU-Pants + Tiana 10 Under-Vest (high tension - T#1) - Current Position</t>
+  </si>
+  <si>
+    <t>10. Suit-C3/PU-Pants + Tiana 10 Under-Vest (low tension - T#2) - Current Position</t>
+  </si>
+  <si>
+    <t>11. Suit-C3/PU-Pants + Payen 10 Under-Vest - (high tension - T#1) - Current Position</t>
+  </si>
+  <si>
+    <t>12. Suit-C3/PU-Pants + Payen 15 Under-Vest  - (high tension - T#1) - Current Position</t>
+  </si>
+  <si>
+    <t>13. Suit-C1/PU-Pants + Payen 10 Under-Vest Print 2 (high tension suit - T#2) - Current Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Suit-C1/PU-Pants + Payen 10 Under-Vest Print 4 (high tension suit - T#2) - Current Position </t>
+  </si>
+  <si>
+    <t>15. Suit-C1/PU-Pants + Payen 10 Under-Vest Print 4 (high tension suit - T#2) - Current Position + Miti Overshoes</t>
+  </si>
+  <si>
+    <t>16. Suit-B1/LNM-Pants + Tiana 10 Under-Vest (current)</t>
+  </si>
+  <si>
+    <t>17. Suit-B1/LNM-Pants + Payen 10 Under-Vest (current)</t>
+  </si>
+  <si>
+    <t>18. Repeat Baseline</t>
+  </si>
+  <si>
+    <t>19. Fatigue Positon - Baseline</t>
+  </si>
+  <si>
+    <t>1. Repeat testing of selected suits from May (Le Col Suit - Champion Systems Over Shoes - Evo Pro (M))</t>
+  </si>
+  <si>
+    <t>20. Bike Only</t>
+  </si>
+  <si>
+    <t>0. Bike Only</t>
+  </si>
 </sst>
 </file>
 
@@ -470,7 +536,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -489,6 +555,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -502,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -517,6 +589,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0519FE8-7E25-488D-A25B-6D59627E68B4}">
-  <dimension ref="A1:I517"/>
+  <dimension ref="A1:I665"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.109375" bestFit="1" customWidth="1"/>
@@ -10083,6 +10158,2078 @@
         <v>12</v>
       </c>
     </row>
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>81</v>
+      </c>
+      <c r="G518" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H518">
+        <v>14</v>
+      </c>
+      <c r="I518">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>81</v>
+      </c>
+      <c r="G519" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H519">
+        <v>15</v>
+      </c>
+      <c r="I519">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>81</v>
+      </c>
+      <c r="G520" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H520">
+        <v>16</v>
+      </c>
+      <c r="I520">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>81</v>
+      </c>
+      <c r="G521" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H521">
+        <v>17</v>
+      </c>
+      <c r="I521">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="522" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>81</v>
+      </c>
+      <c r="G522" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H522">
+        <v>18</v>
+      </c>
+      <c r="I522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>81</v>
+      </c>
+      <c r="G523" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H523">
+        <v>19</v>
+      </c>
+      <c r="I523">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
+        <v>81</v>
+      </c>
+      <c r="G524" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H524">
+        <v>20</v>
+      </c>
+      <c r="I524">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>81</v>
+      </c>
+      <c r="G525" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H525">
+        <v>21</v>
+      </c>
+      <c r="I525">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>81</v>
+      </c>
+      <c r="G526" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H526">
+        <v>22</v>
+      </c>
+      <c r="I526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>81</v>
+      </c>
+      <c r="G527" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H527">
+        <v>23</v>
+      </c>
+      <c r="I527">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>81</v>
+      </c>
+      <c r="G528" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H528">
+        <v>24</v>
+      </c>
+      <c r="I528">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>81</v>
+      </c>
+      <c r="G529" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H529">
+        <v>25</v>
+      </c>
+      <c r="I529">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>81</v>
+      </c>
+      <c r="G530" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H530">
+        <v>26</v>
+      </c>
+      <c r="I530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>81</v>
+      </c>
+      <c r="G531" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H531">
+        <v>27</v>
+      </c>
+      <c r="I531">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>81</v>
+      </c>
+      <c r="G532" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H532">
+        <v>28</v>
+      </c>
+      <c r="I532">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>81</v>
+      </c>
+      <c r="G533" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H533">
+        <v>29</v>
+      </c>
+      <c r="I533">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>81</v>
+      </c>
+      <c r="G534" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H534">
+        <v>30</v>
+      </c>
+      <c r="I534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>81</v>
+      </c>
+      <c r="G535" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H535">
+        <v>31</v>
+      </c>
+      <c r="I535">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>81</v>
+      </c>
+      <c r="G536" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H536">
+        <v>32</v>
+      </c>
+      <c r="I536">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>81</v>
+      </c>
+      <c r="G537" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H537">
+        <v>33</v>
+      </c>
+      <c r="I537">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>81</v>
+      </c>
+      <c r="G538" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H538">
+        <v>34</v>
+      </c>
+      <c r="I538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>81</v>
+      </c>
+      <c r="G539" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H539">
+        <v>35</v>
+      </c>
+      <c r="I539">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>81</v>
+      </c>
+      <c r="G540" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H540">
+        <v>36</v>
+      </c>
+      <c r="I540">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>81</v>
+      </c>
+      <c r="G541" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H541">
+        <v>37</v>
+      </c>
+      <c r="I541">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>81</v>
+      </c>
+      <c r="G542" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H542">
+        <v>38</v>
+      </c>
+      <c r="I542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>81</v>
+      </c>
+      <c r="G543" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H543">
+        <v>39</v>
+      </c>
+      <c r="I543">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>81</v>
+      </c>
+      <c r="G544" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H544">
+        <v>40</v>
+      </c>
+      <c r="I544">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>81</v>
+      </c>
+      <c r="G545" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H545">
+        <v>41</v>
+      </c>
+      <c r="I545">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>81</v>
+      </c>
+      <c r="G546" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H546">
+        <v>42</v>
+      </c>
+      <c r="I546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>81</v>
+      </c>
+      <c r="G547" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H547">
+        <v>43</v>
+      </c>
+      <c r="I547">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>81</v>
+      </c>
+      <c r="G548" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H548">
+        <v>44</v>
+      </c>
+      <c r="I548">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>81</v>
+      </c>
+      <c r="G549" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H549">
+        <v>45</v>
+      </c>
+      <c r="I549">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>81</v>
+      </c>
+      <c r="G550" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H550">
+        <v>46</v>
+      </c>
+      <c r="I550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>81</v>
+      </c>
+      <c r="G551" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H551">
+        <v>47</v>
+      </c>
+      <c r="I551">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="552" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>81</v>
+      </c>
+      <c r="G552" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H552">
+        <v>48</v>
+      </c>
+      <c r="I552">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>81</v>
+      </c>
+      <c r="G553" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H553">
+        <v>49</v>
+      </c>
+      <c r="I553">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>81</v>
+      </c>
+      <c r="G554" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H554">
+        <v>50</v>
+      </c>
+      <c r="I554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>81</v>
+      </c>
+      <c r="G555" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H555">
+        <v>51</v>
+      </c>
+      <c r="I555">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>81</v>
+      </c>
+      <c r="G556" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H556">
+        <v>52</v>
+      </c>
+      <c r="I556">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>81</v>
+      </c>
+      <c r="G557" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H557">
+        <v>53</v>
+      </c>
+      <c r="I557">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>81</v>
+      </c>
+      <c r="G558" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H558">
+        <v>54</v>
+      </c>
+      <c r="I558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>81</v>
+      </c>
+      <c r="G559" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H559">
+        <v>55</v>
+      </c>
+      <c r="I559">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>81</v>
+      </c>
+      <c r="G560" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H560">
+        <v>56</v>
+      </c>
+      <c r="I560">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>81</v>
+      </c>
+      <c r="G561" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H561">
+        <v>57</v>
+      </c>
+      <c r="I561">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>81</v>
+      </c>
+      <c r="G562" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H562">
+        <v>58</v>
+      </c>
+      <c r="I562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>81</v>
+      </c>
+      <c r="G563" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H563">
+        <v>59</v>
+      </c>
+      <c r="I563">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>81</v>
+      </c>
+      <c r="G564" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H564">
+        <v>60</v>
+      </c>
+      <c r="I564">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>81</v>
+      </c>
+      <c r="G565" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H565">
+        <v>61</v>
+      </c>
+      <c r="I565">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>81</v>
+      </c>
+      <c r="G566" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H566">
+        <v>62</v>
+      </c>
+      <c r="I566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>81</v>
+      </c>
+      <c r="G567" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H567">
+        <v>63</v>
+      </c>
+      <c r="I567">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>81</v>
+      </c>
+      <c r="G568" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H568">
+        <v>64</v>
+      </c>
+      <c r="I568">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>81</v>
+      </c>
+      <c r="G569" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H569">
+        <v>65</v>
+      </c>
+      <c r="I569">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>81</v>
+      </c>
+      <c r="G570" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H570">
+        <v>67</v>
+      </c>
+      <c r="I570">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>81</v>
+      </c>
+      <c r="G571" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H571">
+        <v>68</v>
+      </c>
+      <c r="I571">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>81</v>
+      </c>
+      <c r="G572" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H572">
+        <v>69</v>
+      </c>
+      <c r="I572">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="573" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>81</v>
+      </c>
+      <c r="G573" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H573">
+        <v>70</v>
+      </c>
+      <c r="I573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>81</v>
+      </c>
+      <c r="G574" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H574">
+        <v>71</v>
+      </c>
+      <c r="I574">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="575" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>81</v>
+      </c>
+      <c r="G575" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H575">
+        <v>72</v>
+      </c>
+      <c r="I575">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="576" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>81</v>
+      </c>
+      <c r="G576" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H576">
+        <v>73</v>
+      </c>
+      <c r="I576">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>81</v>
+      </c>
+      <c r="G577" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H577">
+        <v>74</v>
+      </c>
+      <c r="I577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>81</v>
+      </c>
+      <c r="G578" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H578">
+        <v>75</v>
+      </c>
+      <c r="I578">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>81</v>
+      </c>
+      <c r="G579" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H579">
+        <v>76</v>
+      </c>
+      <c r="I579">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>81</v>
+      </c>
+      <c r="G580" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H580">
+        <v>77</v>
+      </c>
+      <c r="I580">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>81</v>
+      </c>
+      <c r="G581" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H581">
+        <v>78</v>
+      </c>
+      <c r="I581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>81</v>
+      </c>
+      <c r="G582" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H582">
+        <v>79</v>
+      </c>
+      <c r="I582">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>81</v>
+      </c>
+      <c r="G583" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H583">
+        <v>80</v>
+      </c>
+      <c r="I583">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A584" t="s">
+        <v>81</v>
+      </c>
+      <c r="G584" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H584">
+        <v>81</v>
+      </c>
+      <c r="I584">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>81</v>
+      </c>
+      <c r="G585" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H585">
+        <v>82</v>
+      </c>
+      <c r="I585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
+        <v>81</v>
+      </c>
+      <c r="G586" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H586">
+        <v>83</v>
+      </c>
+      <c r="I586">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A587" t="s">
+        <v>81</v>
+      </c>
+      <c r="G587" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H587">
+        <v>84</v>
+      </c>
+      <c r="I587">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A588" t="s">
+        <v>81</v>
+      </c>
+      <c r="G588" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H588">
+        <v>85</v>
+      </c>
+      <c r="I588">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A589" t="s">
+        <v>81</v>
+      </c>
+      <c r="G589" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H589">
+        <v>86</v>
+      </c>
+      <c r="I589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A590" t="s">
+        <v>81</v>
+      </c>
+      <c r="G590" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H590">
+        <v>87</v>
+      </c>
+      <c r="I590">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A591" t="s">
+        <v>81</v>
+      </c>
+      <c r="G591" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H591">
+        <v>88</v>
+      </c>
+      <c r="I591">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A592" t="s">
+        <v>81</v>
+      </c>
+      <c r="G592" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H592">
+        <v>89</v>
+      </c>
+      <c r="I592">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A593" t="s">
+        <v>81</v>
+      </c>
+      <c r="G593" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H593">
+        <v>90</v>
+      </c>
+      <c r="I593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A594" t="s">
+        <v>81</v>
+      </c>
+      <c r="G594" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H594">
+        <v>91</v>
+      </c>
+      <c r="I594">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A595" t="s">
+        <v>81</v>
+      </c>
+      <c r="G595" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H595">
+        <v>92</v>
+      </c>
+      <c r="I595">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A596" t="s">
+        <v>81</v>
+      </c>
+      <c r="G596" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H596">
+        <v>93</v>
+      </c>
+      <c r="I596">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A597" t="s">
+        <v>81</v>
+      </c>
+      <c r="G597" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H597">
+        <v>94</v>
+      </c>
+      <c r="I597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A598" t="s">
+        <v>81</v>
+      </c>
+      <c r="G598" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H598">
+        <v>95</v>
+      </c>
+      <c r="I598">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A599" t="s">
+        <v>81</v>
+      </c>
+      <c r="G599" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H599">
+        <v>96</v>
+      </c>
+      <c r="I599">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A600" t="s">
+        <v>81</v>
+      </c>
+      <c r="G600" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H600">
+        <v>97</v>
+      </c>
+      <c r="I600">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A601" t="s">
+        <v>81</v>
+      </c>
+      <c r="G601" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H601">
+        <v>98</v>
+      </c>
+      <c r="I601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A602" t="s">
+        <v>81</v>
+      </c>
+      <c r="G602" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H602">
+        <v>99</v>
+      </c>
+      <c r="I602">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A603" t="s">
+        <v>81</v>
+      </c>
+      <c r="G603" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H603">
+        <v>100</v>
+      </c>
+      <c r="I603">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A604" t="s">
+        <v>81</v>
+      </c>
+      <c r="G604" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H604">
+        <v>101</v>
+      </c>
+      <c r="I604">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A605" t="s">
+        <v>81</v>
+      </c>
+      <c r="G605" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H605">
+        <v>102</v>
+      </c>
+      <c r="I605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A606" t="s">
+        <v>81</v>
+      </c>
+      <c r="G606" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H606">
+        <v>103</v>
+      </c>
+      <c r="I606">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A607" t="s">
+        <v>81</v>
+      </c>
+      <c r="G607" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H607">
+        <v>104</v>
+      </c>
+      <c r="I607">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A608" t="s">
+        <v>81</v>
+      </c>
+      <c r="G608" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H608">
+        <v>105</v>
+      </c>
+      <c r="I608">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A609" t="s">
+        <v>81</v>
+      </c>
+      <c r="G609" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H609">
+        <v>106</v>
+      </c>
+      <c r="I609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A610" t="s">
+        <v>81</v>
+      </c>
+      <c r="G610" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H610">
+        <v>107</v>
+      </c>
+      <c r="I610">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A611" t="s">
+        <v>81</v>
+      </c>
+      <c r="G611" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H611">
+        <v>108</v>
+      </c>
+      <c r="I611">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A612" t="s">
+        <v>81</v>
+      </c>
+      <c r="G612" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H612">
+        <v>109</v>
+      </c>
+      <c r="I612">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A613" t="s">
+        <v>81</v>
+      </c>
+      <c r="G613" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H613">
+        <v>110</v>
+      </c>
+      <c r="I613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A614" t="s">
+        <v>81</v>
+      </c>
+      <c r="G614" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H614">
+        <v>111</v>
+      </c>
+      <c r="I614">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A615" t="s">
+        <v>81</v>
+      </c>
+      <c r="G615" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H615">
+        <v>112</v>
+      </c>
+      <c r="I615">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A616" t="s">
+        <v>81</v>
+      </c>
+      <c r="G616" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H616">
+        <v>113</v>
+      </c>
+      <c r="I616">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A617" t="s">
+        <v>81</v>
+      </c>
+      <c r="G617" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H617">
+        <v>114</v>
+      </c>
+      <c r="I617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A618" t="s">
+        <v>81</v>
+      </c>
+      <c r="G618" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H618">
+        <v>115</v>
+      </c>
+      <c r="I618">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A619" t="s">
+        <v>81</v>
+      </c>
+      <c r="G619" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H619">
+        <v>117</v>
+      </c>
+      <c r="I619">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A620" t="s">
+        <v>81</v>
+      </c>
+      <c r="G620" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H620">
+        <v>118</v>
+      </c>
+      <c r="I620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A621" t="s">
+        <v>81</v>
+      </c>
+      <c r="G621" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H621">
+        <v>119</v>
+      </c>
+      <c r="I621">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A622" t="s">
+        <v>81</v>
+      </c>
+      <c r="G622" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H622">
+        <v>120</v>
+      </c>
+      <c r="I622">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A623" t="s">
+        <v>81</v>
+      </c>
+      <c r="G623" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H623">
+        <v>121</v>
+      </c>
+      <c r="I623">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A624" t="s">
+        <v>81</v>
+      </c>
+      <c r="G624" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H624">
+        <v>122</v>
+      </c>
+      <c r="I624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A625" t="s">
+        <v>81</v>
+      </c>
+      <c r="G625" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H625">
+        <v>123</v>
+      </c>
+      <c r="I625">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A626" t="s">
+        <v>81</v>
+      </c>
+      <c r="G626" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H626">
+        <v>124</v>
+      </c>
+      <c r="I626">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A627" t="s">
+        <v>81</v>
+      </c>
+      <c r="G627" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H627">
+        <v>125</v>
+      </c>
+      <c r="I627">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A628" t="s">
+        <v>81</v>
+      </c>
+      <c r="G628" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H628">
+        <v>126</v>
+      </c>
+      <c r="I628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A629" t="s">
+        <v>81</v>
+      </c>
+      <c r="G629" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H629">
+        <v>127</v>
+      </c>
+      <c r="I629">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A630" t="s">
+        <v>81</v>
+      </c>
+      <c r="G630" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H630">
+        <v>128</v>
+      </c>
+      <c r="I630">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A631" t="s">
+        <v>81</v>
+      </c>
+      <c r="G631" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H631">
+        <v>129</v>
+      </c>
+      <c r="I631">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A632" t="s">
+        <v>81</v>
+      </c>
+      <c r="G632" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H632">
+        <v>130</v>
+      </c>
+      <c r="I632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A633" t="s">
+        <v>81</v>
+      </c>
+      <c r="G633" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H633">
+        <v>131</v>
+      </c>
+      <c r="I633">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A634" t="s">
+        <v>81</v>
+      </c>
+      <c r="G634" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H634">
+        <v>132</v>
+      </c>
+      <c r="I634">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A635" t="s">
+        <v>81</v>
+      </c>
+      <c r="G635" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H635">
+        <v>133</v>
+      </c>
+      <c r="I635">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A636" t="s">
+        <v>81</v>
+      </c>
+      <c r="G636" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H636">
+        <v>134</v>
+      </c>
+      <c r="I636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A637" t="s">
+        <v>81</v>
+      </c>
+      <c r="G637" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H637">
+        <v>135</v>
+      </c>
+      <c r="I637">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A638" t="s">
+        <v>81</v>
+      </c>
+      <c r="G638" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H638">
+        <v>136</v>
+      </c>
+      <c r="I638">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A639" t="s">
+        <v>81</v>
+      </c>
+      <c r="G639" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H639">
+        <v>137</v>
+      </c>
+      <c r="I639">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A640" t="s">
+        <v>81</v>
+      </c>
+      <c r="G640" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H640">
+        <v>138</v>
+      </c>
+      <c r="I640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A641" t="s">
+        <v>81</v>
+      </c>
+      <c r="G641" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H641">
+        <v>139</v>
+      </c>
+      <c r="I641">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A642" t="s">
+        <v>81</v>
+      </c>
+      <c r="G642" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H642">
+        <v>140</v>
+      </c>
+      <c r="I642">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A643" t="s">
+        <v>81</v>
+      </c>
+      <c r="G643" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H643">
+        <v>141</v>
+      </c>
+      <c r="I643">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A644" t="s">
+        <v>81</v>
+      </c>
+      <c r="G644" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H644">
+        <v>142</v>
+      </c>
+      <c r="I644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A645" t="s">
+        <v>81</v>
+      </c>
+      <c r="G645" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H645">
+        <v>143</v>
+      </c>
+      <c r="I645">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="646" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A646" t="s">
+        <v>81</v>
+      </c>
+      <c r="G646" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H646">
+        <v>144</v>
+      </c>
+      <c r="I646">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="647" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A647" t="s">
+        <v>81</v>
+      </c>
+      <c r="G647" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H647">
+        <v>145</v>
+      </c>
+      <c r="I647">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="648" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A648" t="s">
+        <v>81</v>
+      </c>
+      <c r="G648" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H648">
+        <v>146</v>
+      </c>
+      <c r="I648">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A649" t="s">
+        <v>81</v>
+      </c>
+      <c r="G649" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H649">
+        <v>147</v>
+      </c>
+      <c r="I649">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="650" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A650" t="s">
+        <v>81</v>
+      </c>
+      <c r="G650" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H650">
+        <v>148</v>
+      </c>
+      <c r="I650">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="651" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>81</v>
+      </c>
+      <c r="G651" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H651">
+        <v>149</v>
+      </c>
+      <c r="I651">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="652" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>81</v>
+      </c>
+      <c r="G652" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H652">
+        <v>150</v>
+      </c>
+      <c r="I652">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>81</v>
+      </c>
+      <c r="G653" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H653">
+        <v>151</v>
+      </c>
+      <c r="I653">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="654" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A654" t="s">
+        <v>81</v>
+      </c>
+      <c r="G654" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H654">
+        <v>152</v>
+      </c>
+      <c r="I654">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="655" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A655" t="s">
+        <v>81</v>
+      </c>
+      <c r="G655" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H655">
+        <v>153</v>
+      </c>
+      <c r="I655">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="656" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A656" t="s">
+        <v>81</v>
+      </c>
+      <c r="G656" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H656">
+        <v>154</v>
+      </c>
+      <c r="I656">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A657" t="s">
+        <v>81</v>
+      </c>
+      <c r="G657" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H657">
+        <v>155</v>
+      </c>
+      <c r="I657">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="658" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A658" t="s">
+        <v>81</v>
+      </c>
+      <c r="G658" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H658">
+        <v>156</v>
+      </c>
+      <c r="I658">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="659" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A659" t="s">
+        <v>81</v>
+      </c>
+      <c r="G659" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H659">
+        <v>157</v>
+      </c>
+      <c r="I659">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="660" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A660" t="s">
+        <v>81</v>
+      </c>
+      <c r="G660" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H660">
+        <v>158</v>
+      </c>
+      <c r="I660">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A661" t="s">
+        <v>81</v>
+      </c>
+      <c r="G661" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H661">
+        <v>159</v>
+      </c>
+      <c r="I661">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="662" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A662" t="s">
+        <v>81</v>
+      </c>
+      <c r="G662" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H662">
+        <v>160</v>
+      </c>
+      <c r="I662">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="663" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A663" t="s">
+        <v>81</v>
+      </c>
+      <c r="G663" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H663">
+        <v>161</v>
+      </c>
+      <c r="I663">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="664" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A664" t="s">
+        <v>81</v>
+      </c>
+      <c r="G664" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H664">
+        <v>162</v>
+      </c>
+      <c r="I664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A665" t="s">
+        <v>81</v>
+      </c>
+      <c r="G665" t="s">
+        <v>101</v>
+      </c>
+      <c r="H665">
+        <v>163</v>
+      </c>
+      <c r="I665">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/CdA Testing/FullRunSheet.xlsx
+++ b/pages/CdA Testing/FullRunSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C8B74C-BCC9-4F0D-A94C-AF57915AFDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AF164E-FB75-489A-BCFA-D118C2AE60CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10704" yWindow="0" windowWidth="12300" windowHeight="12504" xr2:uid="{C4EF7516-2B37-40B4-B22F-A762B428A288}"/>
+    <workbookView xWindow="37800" yWindow="2250" windowWidth="10800" windowHeight="12525" xr2:uid="{C4EF7516-2B37-40B4-B22F-A762B428A288}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/pages/CdA Testing/FullRunSheet.xlsx
+++ b/pages/CdA Testing/FullRunSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AF164E-FB75-489A-BCFA-D118C2AE60CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E103318-0134-44E7-99FF-AE372812AABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37800" yWindow="2250" windowWidth="10800" windowHeight="12525" xr2:uid="{C4EF7516-2B37-40B4-B22F-A762B428A288}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{C4EF7516-2B37-40B4-B22F-A762B428A288}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="108">
   <si>
     <t>Album</t>
   </si>
@@ -496,6 +496,21 @@
   <si>
     <t>0. Bike Only</t>
   </si>
+  <si>
+    <t>23-11-27 Ellesse Andrews Bike Fit</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Seat up 5mm</t>
+  </si>
+  <si>
+    <t>Seat up 7.5mm</t>
+  </si>
+  <si>
+    <t>Seat up 10mm</t>
+  </si>
 </sst>
 </file>
 
@@ -906,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0519FE8-7E25-488D-A25B-6D59627E68B4}">
-  <dimension ref="A1:I665"/>
+  <dimension ref="A1:I669"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.109375" bestFit="1" customWidth="1"/>
@@ -12230,6 +12245,38 @@
         <v>13</v>
       </c>
     </row>
+    <row r="666" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A666" t="s">
+        <v>103</v>
+      </c>
+      <c r="B666" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="667" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A667" t="s">
+        <v>103</v>
+      </c>
+      <c r="B667" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="668" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A668" t="s">
+        <v>103</v>
+      </c>
+      <c r="B668" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="669" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A669" t="s">
+        <v>103</v>
+      </c>
+      <c r="B669" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
